--- a/test_git.xlsx
+++ b/test_git.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s.galas\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Inne\IT_tutorial_R\Power BI\mapy_topojson\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C373DC42-D033-4C56-8F1A-58AFBD6FC79F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECE2B064-0680-4474-A106-9C81EDE7EECE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{1A46E72F-CD85-4446-BD14-2EC9FF3EA193}"/>
   </bookViews>
@@ -36,15 +36,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>Location</t>
-  </si>
-  <si>
-    <t>Pakownia B</t>
-  </si>
-  <si>
-    <t>Warsztat</t>
   </si>
   <si>
     <t>Logistyka</t>
@@ -57,9 +51,6 @@
   </si>
   <si>
     <t>Pakownia_A</t>
-  </si>
-  <si>
-    <t>Brak</t>
   </si>
 </sst>
 </file>
@@ -432,7 +423,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9FD110B-D820-436B-9D6C-D21B182E8667}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.21875" bestFit="1" customWidth="1"/>
@@ -443,12 +434,12 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -459,7 +450,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -467,28 +458,7 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6">
         <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
